--- a/grupos/2ASV - Estadisticos 20212.xlsx
+++ b/grupos/2ASV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="99">
   <si>
     <t>Materia</t>
   </si>
@@ -149,15 +149,15 @@
     <t>González Nuñez Veronica</t>
   </si>
   <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -170,6 +170,15 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ALEXIS ISAI</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
@@ -182,18 +191,12 @@
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
     <t>MOTA</t>
   </si>
   <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -206,12 +209,18 @@
     <t>REYES</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>SALAZAR</t>
   </si>
   <si>
     <t>TEMOXTLE</t>
   </si>
   <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
@@ -248,7 +257,7 @@
     <t>GALICIA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>CRUZ</t>
   </si>
   <si>
     <t>GARCIA</t>
@@ -281,9 +290,6 @@
     <t>ISAAC</t>
   </si>
   <si>
-    <t>ALEXIS ISAI</t>
-  </si>
-  <si>
     <t>DAVID</t>
   </si>
   <si>
@@ -299,19 +305,13 @@
     <t>LUIS ANGEL</t>
   </si>
   <si>
+    <t>FERNANDO ANGEL</t>
+  </si>
+  <si>
     <t>LUIS GUILLERMO</t>
   </si>
   <si>
     <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>DE LA TEJA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FERNANDO ANGEL</t>
   </si>
   <si>
     <t>KEVIN GABRIEL</t>
@@ -803,7 +803,7 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>7</v>
@@ -857,7 +857,7 @@
         <v>5</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -880,7 +880,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>10</v>
@@ -934,7 +934,7 @@
         <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -986,7 +986,7 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -1040,7 +1040,7 @@
         <v>8</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1063,7 +1063,7 @@
         <v>8</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1117,7 +1117,7 @@
         <v>8</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -1140,7 +1140,7 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D9">
         <v>6</v>
@@ -1194,7 +1194,7 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>6</v>
@@ -1217,13 +1217,13 @@
         <v>8</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>9</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F10">
         <v>6</v>
@@ -1271,13 +1271,13 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1294,7 +1294,7 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1321,7 +1321,7 @@
         <v>6</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1335,7 +1335,7 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>9</v>
@@ -1389,7 +1389,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1412,7 +1412,7 @@
         <v>9</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>8</v>
@@ -1466,7 +1466,7 @@
         <v>9</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>8</v>
@@ -1489,7 +1489,7 @@
         <v>5</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D14">
         <v>8</v>
@@ -1543,7 +1543,7 @@
         <v>5</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1566,7 +1566,7 @@
         <v>8</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D15">
         <v>10</v>
@@ -1620,7 +1620,7 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>10</v>
@@ -1643,7 +1643,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>7</v>
@@ -1697,7 +1697,7 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1720,7 +1720,7 @@
         <v>5</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>8</v>
@@ -1774,7 +1774,7 @@
         <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -1797,7 +1797,7 @@
         <v>6</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D18">
         <v>10</v>
@@ -1851,7 +1851,7 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>10</v>
@@ -1874,7 +1874,7 @@
         <v>8</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D19">
         <v>9</v>
@@ -1928,7 +1928,7 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>9</v>
@@ -1951,7 +1951,7 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -2005,7 +2005,7 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2057,7 +2057,7 @@
         <v>7</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <v>9</v>
@@ -2111,7 +2111,7 @@
         <v>7</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2188,22 +2188,25 @@
         <v>17</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>70.59</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>29.41</v>
+      </c>
+      <c r="H2">
+        <v>5.7</v>
       </c>
       <c r="I2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2272,39 +2275,39 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>43</v>
       </c>
       <c r="C5">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>44</v>
@@ -2325,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2336,16 +2339,16 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>45</v>
       </c>
       <c r="C7">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -2357,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2373,7 +2376,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2402,382 +2405,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920135</v>
+        <v>21330051920145</v>
       </c>
       <c r="B2" t="s">
         <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920138</v>
-      </c>
-      <c r="B3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920139</v>
-      </c>
-      <c r="B4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920140</v>
-      </c>
-      <c r="B5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051650295</v>
-      </c>
-      <c r="B6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920141</v>
-      </c>
-      <c r="B7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920141</v>
-      </c>
-      <c r="B8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>18330051920404</v>
-      </c>
-      <c r="B9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920143</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920381</v>
-      </c>
-      <c r="B11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920145</v>
-      </c>
-      <c r="B12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920145</v>
-      </c>
-      <c r="B13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920146</v>
-      </c>
-      <c r="B14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920395</v>
-      </c>
-      <c r="B15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920147</v>
-      </c>
-      <c r="B16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920148</v>
-      </c>
-      <c r="B17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" t="s">
-        <v>91</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920150</v>
-      </c>
-      <c r="B18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" t="s">
-        <v>92</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920382</v>
-      </c>
-      <c r="B19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920392</v>
-      </c>
-      <c r="B20" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" t="s">
-        <v>94</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2813,121 +2456,121 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920141</v>
+        <v>21330051920145</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920145</v>
+        <v>21330051920135</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920135</v>
+        <v>21330051920138</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920138</v>
+        <v>21330051920139</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920139</v>
+        <v>21330051920140</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920140</v>
+        <v>21330051650295</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051650295</v>
+        <v>21330051920141</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2935,16 +2578,16 @@
         <v>18330051920404</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2952,16 +2595,16 @@
         <v>21330051920143</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2969,16 +2612,16 @@
         <v>21330051920381</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2986,16 +2629,16 @@
         <v>21330051920146</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3003,16 +2646,16 @@
         <v>21330051920395</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3020,16 +2663,16 @@
         <v>21330051920147</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3037,16 +2680,16 @@
         <v>21330051920148</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3054,61 +2697,61 @@
         <v>21330051920150</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920382</v>
+        <v>18330051920413</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920392</v>
+        <v>21330051920382</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>18330051920413</v>
+        <v>21330051920392</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
         <v>97</v>
@@ -3122,10 +2765,10 @@
         <v>18330051920388</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
         <v>98</v>
@@ -3141,7 +2784,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3173,45 +2816,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920141</v>
+        <v>21330051920145</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920141</v>
+        <v>21330051920145</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -3222,13 +2865,13 @@
         <v>21330051920147</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -3245,13 +2888,13 @@
         <v>21330051920147</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -3260,27 +2903,27 @@
         <v>40</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920382</v>
+        <v>21330051920141</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3288,16 +2931,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920382</v>
+        <v>21330051920143</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -3306,21 +2949,21 @@
         <v>40</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920138</v>
+        <v>21330051920381</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -3329,260 +2972,30 @@
         <v>40</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920139</v>
+        <v>21330051920382</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920140</v>
-      </c>
-      <c r="B10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051650295</v>
-      </c>
-      <c r="B11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>18330051920404</v>
-      </c>
-      <c r="B12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920143</v>
-      </c>
-      <c r="B13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>40</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920381</v>
-      </c>
-      <c r="B14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920146</v>
-      </c>
-      <c r="B15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>40</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920395</v>
-      </c>
-      <c r="B16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" t="s">
-        <v>73</v>
-      </c>
-      <c r="D16" t="s">
-        <v>89</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>40</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920148</v>
-      </c>
-      <c r="B17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" t="s">
-        <v>91</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>40</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920150</v>
-      </c>
-      <c r="B18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" t="s">
-        <v>92</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>40</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920392</v>
-      </c>
-      <c r="B19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" t="s">
-        <v>94</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>40</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2ASV - Estadisticos 20212.xlsx
+++ b/grupos/2ASV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="99">
   <si>
     <t>Materia</t>
   </si>
@@ -143,13 +143,13 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
     <t>Pesce Bautista Victor Manuel</t>
@@ -818,22 +818,22 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -854,22 +854,22 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>5</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -895,22 +895,22 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -931,7 +931,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>6</v>
@@ -960,10 +960,10 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1001,22 +1001,22 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1052,7 +1052,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1078,22 +1078,22 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1155,22 +1155,22 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1191,16 +1191,16 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>6</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -1232,22 +1232,22 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1268,7 +1268,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1283,7 +1283,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1300,13 +1300,13 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1350,22 +1350,22 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1386,7 +1386,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>5</v>
@@ -1401,7 +1401,7 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1427,22 +1427,22 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1463,7 +1463,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -1478,7 +1478,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1510,10 +1510,10 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1549,7 +1549,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>-1</v>
@@ -1581,22 +1581,22 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1617,7 +1617,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>6</v>
@@ -1626,13 +1626,13 @@
         <v>10</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1658,22 +1658,22 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1694,7 +1694,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>6</v>
@@ -1703,7 +1703,7 @@
         <v>7</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -1735,22 +1735,22 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1771,13 +1771,13 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>5</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -1786,7 +1786,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1812,22 +1812,22 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1848,7 +1848,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>6</v>
@@ -1863,7 +1863,7 @@
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1889,22 +1889,22 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1925,7 +1925,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>6</v>
@@ -1940,7 +1940,7 @@
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1966,22 +1966,22 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2002,22 +2002,22 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>6</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X20">
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2031,10 +2031,10 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2043,7 +2043,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2072,22 +2072,22 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2108,7 +2108,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>6</v>
@@ -2211,39 +2211,39 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>41</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>78.95</v>
+        <v>87.5</v>
       </c>
       <c r="G3">
-        <v>21.05</v>
+        <v>6.25</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>42</v>
@@ -2252,51 +2252,51 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>87.5</v>
+        <v>93.75</v>
       </c>
       <c r="G4">
         <v>6.25</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>43</v>
       </c>
       <c r="C5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2328,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2360,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2420,7 +2420,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2784,7 +2784,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2816,22 +2816,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920145</v>
+        <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -2839,45 +2839,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920145</v>
+        <v>21330051920135</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920147</v>
+        <v>21330051920145</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -2885,25 +2885,25 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920147</v>
+        <v>21330051920145</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2977,24 +2977,47 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
+        <v>21330051920147</v>
+      </c>
+      <c r="B9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
         <v>21330051920382</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>64</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>51</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
         <v>96</v>
       </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9">
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ASV - Estadisticos 20212.xlsx
+++ b/grupos/2ASV - Estadisticos 20212.xlsx
@@ -821,7 +821,7 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>8</v>
@@ -898,7 +898,7 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -1004,7 +1004,7 @@
         <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>9</v>
@@ -1081,7 +1081,7 @@
         <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1158,7 +1158,7 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>8</v>
@@ -1584,7 +1584,7 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>10</v>
@@ -1661,7 +1661,7 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>7</v>
@@ -1738,7 +1738,7 @@
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>9</v>
@@ -1815,7 +1815,7 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>10</v>
@@ -1892,7 +1892,7 @@
         <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>9</v>
@@ -1969,7 +1969,7 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <v>8</v>
@@ -2075,7 +2075,7 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>8</v>

--- a/grupos/2ASV - Estadisticos 20212.xlsx
+++ b/grupos/2ASV - Estadisticos 20212.xlsx
@@ -830,7 +830,7 @@
         <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>5</v>
@@ -907,7 +907,7 @@
         <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -1013,7 +1013,7 @@
         <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>9</v>
@@ -1090,7 +1090,7 @@
         <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>8</v>
@@ -1167,7 +1167,7 @@
         <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -1244,7 +1244,7 @@
         <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>7</v>
@@ -1280,7 +1280,7 @@
         <v>6</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -1362,7 +1362,7 @@
         <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>5</v>
@@ -1439,7 +1439,7 @@
         <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>7</v>
@@ -1475,7 +1475,7 @@
         <v>9</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>8</v>
@@ -1593,7 +1593,7 @@
         <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>8</v>
@@ -1670,7 +1670,7 @@
         <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
         <v>9</v>
@@ -1706,7 +1706,7 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1824,7 +1824,7 @@
         <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>8</v>
@@ -1860,7 +1860,7 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -1901,7 +1901,7 @@
         <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>10</v>
@@ -1978,7 +1978,7 @@
         <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -2014,7 +2014,7 @@
         <v>10</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2084,7 +2084,7 @@
         <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -2120,7 +2120,7 @@
         <v>9</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y22">
         <v>10</v>

--- a/grupos/2ASV - Estadisticos 20212.xlsx
+++ b/grupos/2ASV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="99">
   <si>
     <t>Materia</t>
   </si>
@@ -146,12 +146,12 @@
     <t>González Nuñez Veronica</t>
   </si>
   <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -170,124 +170,124 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>ILLESCAS</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>CONSTANTINO</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>RIVADENEYRA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>JOSE RUBEN</t>
+  </si>
+  <si>
+    <t>CRISTHIAN ALFONSO</t>
+  </si>
+  <si>
+    <t>MILKA SARAY</t>
+  </si>
+  <si>
+    <t>REDA ALAN</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
   </si>
   <si>
     <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>DE LA TEJA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>ILLESCAS</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>CONSTANTINO</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>RIVADENEYRA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>JOSE RUBEN</t>
-  </si>
-  <si>
-    <t>CRISTHIAN ALFONSO</t>
-  </si>
-  <si>
-    <t>MILKA SARAY</t>
-  </si>
-  <si>
-    <t>REDA ALAN</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
   </si>
   <si>
     <t>DAVID</t>
@@ -842,16 +842,16 @@
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>7</v>
@@ -866,7 +866,7 @@
         <v>7</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -919,16 +919,16 @@
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -1025,16 +1025,16 @@
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -1102,16 +1102,16 @@
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>8</v>
@@ -1120,7 +1120,7 @@
         <v>6</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1179,16 +1179,16 @@
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>9</v>
@@ -1235,7 +1235,7 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>9</v>
@@ -1256,16 +1256,16 @@
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1283,7 +1283,7 @@
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1303,7 +1303,7 @@
         <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>9</v>
@@ -1353,7 +1353,7 @@
         <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>8</v>
@@ -1374,16 +1374,16 @@
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>8</v>
@@ -1430,7 +1430,7 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
         <v>8</v>
@@ -1451,16 +1451,16 @@
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -1478,7 +1478,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1498,7 +1498,7 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G14">
         <v>9</v>
@@ -1519,7 +1519,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1528,7 +1528,7 @@
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1537,7 +1537,7 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>5</v>
@@ -1546,16 +1546,16 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>8</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1605,16 +1605,16 @@
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1682,16 +1682,16 @@
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>8</v>
@@ -1706,10 +1706,10 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1747,7 +1747,7 @@
         <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
         <v>9</v>
@@ -1759,16 +1759,16 @@
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -1786,7 +1786,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1836,16 +1836,16 @@
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>8</v>
@@ -1860,10 +1860,10 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1913,16 +1913,16 @@
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -1990,16 +1990,16 @@
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>8</v>
@@ -2017,7 +2017,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2096,16 +2096,16 @@
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>8</v>
@@ -2114,13 +2114,13 @@
         <v>6</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>9</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>10</v>
@@ -2220,51 +2220,51 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>87.5</v>
+        <v>93.75</v>
       </c>
       <c r="G3">
         <v>6.25</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>42</v>
       </c>
       <c r="C4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>93.75</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="G4">
-        <v>6.25</v>
+        <v>5.26</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2275,28 +2275,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>43</v>
       </c>
       <c r="C5">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2328,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2376,7 +2376,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2401,26 +2401,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920145</v>
-      </c>
-      <c r="B2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2456,27 +2436,27 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920145</v>
+        <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
         <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920135</v>
+        <v>21330051920138</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
         <v>67</v>
@@ -2490,10 +2470,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920138</v>
+        <v>21330051920139</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
         <v>68</v>
@@ -2507,13 +2487,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920139</v>
+        <v>21330051920140</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
         <v>83</v>
@@ -2524,13 +2504,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920140</v>
+        <v>21330051650295</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
         <v>84</v>
@@ -2541,10 +2521,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051650295</v>
+        <v>21330051920141</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
         <v>70</v>
@@ -2558,10 +2538,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920141</v>
+        <v>18330051920404</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
         <v>71</v>
@@ -2575,10 +2555,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>18330051920404</v>
+        <v>21330051920143</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
         <v>72</v>
@@ -2592,10 +2572,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920143</v>
+        <v>21330051920381</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
         <v>73</v>
@@ -2609,13 +2589,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920381</v>
+        <v>21330051920145</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
         <v>89</v>
@@ -2629,10 +2609,10 @@
         <v>21330051920146</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
         <v>90</v>
@@ -2646,10 +2626,10 @@
         <v>21330051920395</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
         <v>91</v>
@@ -2663,10 +2643,10 @@
         <v>21330051920147</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
         <v>92</v>
@@ -2680,10 +2660,10 @@
         <v>21330051920148</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
         <v>93</v>
@@ -2697,10 +2677,10 @@
         <v>21330051920150</v>
       </c>
       <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" t="s">
         <v>62</v>
-      </c>
-      <c r="C16" t="s">
-        <v>63</v>
       </c>
       <c r="D16" t="s">
         <v>94</v>
@@ -2714,10 +2694,10 @@
         <v>18330051920413</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
         <v>95</v>
@@ -2731,10 +2711,10 @@
         <v>21330051920382</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
         <v>96</v>
@@ -2748,10 +2728,10 @@
         <v>21330051920392</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
         <v>97</v>
@@ -2765,10 +2745,10 @@
         <v>18330051920388</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
         <v>98</v>
@@ -2784,7 +2764,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2816,22 +2796,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920135</v>
+        <v>21330051920145</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -2839,16 +2819,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920135</v>
+        <v>21330051920145</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -2862,22 +2842,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920145</v>
+        <v>21330051920135</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -2885,39 +2865,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920145</v>
+        <v>21330051920141</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920141</v>
+        <v>21330051920143</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -2931,10 +2911,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920143</v>
+        <v>21330051920381</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
         <v>73</v>
@@ -2954,16 +2934,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920381</v>
+        <v>21330051920147</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -2972,52 +2952,6 @@
         <v>40</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920147</v>
-      </c>
-      <c r="B9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920382</v>
-      </c>
-      <c r="B10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ASV - Estadisticos 20212.xlsx
+++ b/grupos/2ASV - Estadisticos 20212.xlsx
@@ -845,7 +845,7 @@
         <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>7</v>
@@ -863,7 +863,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -922,7 +922,7 @@
         <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>9</v>
@@ -969,7 +969,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -1028,7 +1028,7 @@
         <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>8</v>
@@ -1105,7 +1105,7 @@
         <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>10</v>
@@ -1123,7 +1123,7 @@
         <v>6</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1182,7 +1182,7 @@
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>9</v>
@@ -1259,7 +1259,7 @@
         <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>8</v>
@@ -1277,7 +1277,7 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1315,7 +1315,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>6</v>
@@ -1324,7 +1324,7 @@
         <v>6</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>6</v>
@@ -1454,7 +1454,7 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>8</v>
@@ -1531,7 +1531,7 @@
         <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1549,7 +1549,7 @@
         <v>7</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -1608,7 +1608,7 @@
         <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>8</v>
@@ -1685,7 +1685,7 @@
         <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>6</v>
@@ -1762,7 +1762,7 @@
         <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>8</v>
@@ -1839,7 +1839,7 @@
         <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>10</v>
@@ -1916,7 +1916,7 @@
         <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>9</v>
@@ -1993,7 +1993,7 @@
         <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>8</v>
@@ -2040,7 +2040,7 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -2099,7 +2099,7 @@
         <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>8</v>
@@ -2360,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/2ASV - Estadisticos 20212.xlsx
+++ b/grupos/2ASV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="99">
   <si>
     <t>Materia</t>
   </si>
@@ -140,22 +140,22 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
+    <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
     <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
     <t>NC</t>
@@ -836,10 +836,10 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
         <v>8</v>
@@ -854,10 +854,10 @@
         <v>6</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -913,10 +913,10 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
         <v>10</v>
@@ -934,7 +934,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -966,7 +966,7 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>10</v>
@@ -1019,10 +1019,10 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
         <v>9</v>
@@ -1037,7 +1037,7 @@
         <v>9</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>6</v>
@@ -1096,10 +1096,10 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>6</v>
@@ -1114,7 +1114,7 @@
         <v>9</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>6</v>
@@ -1173,10 +1173,10 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>8</v>
@@ -1191,10 +1191,10 @@
         <v>9</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1250,10 +1250,10 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
         <v>9</v>
@@ -1268,10 +1268,10 @@
         <v>7</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -1309,10 +1309,10 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>8</v>
@@ -1368,10 +1368,10 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>9</v>
@@ -1386,10 +1386,10 @@
         <v>6</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1445,10 +1445,10 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>8</v>
@@ -1463,10 +1463,10 @@
         <v>6</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>8</v>
@@ -1504,10 +1504,10 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>8</v>
@@ -1516,16 +1516,16 @@
         <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
         <v>5</v>
@@ -1534,13 +1534,13 @@
         <v>5</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
         <v>5</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>6</v>
@@ -1599,10 +1599,10 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>10</v>
@@ -1617,10 +1617,10 @@
         <v>10</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>10</v>
@@ -1676,10 +1676,10 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>7</v>
@@ -1697,7 +1697,7 @@
         <v>8</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1753,10 +1753,10 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>9</v>
@@ -1771,10 +1771,10 @@
         <v>6</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>9</v>
@@ -1830,10 +1830,10 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
         <v>10</v>
@@ -1848,10 +1848,10 @@
         <v>9</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>10</v>
@@ -1907,10 +1907,10 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>9</v>
@@ -1928,7 +1928,7 @@
         <v>9</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>9</v>
@@ -1984,10 +1984,10 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>8</v>
@@ -2002,7 +2002,7 @@
         <v>7</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>6</v>
@@ -2037,7 +2037,7 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>8</v>
@@ -2090,10 +2090,10 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -2179,28 +2179,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>40</v>
       </c>
       <c r="C2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>70.59</v>
+        <v>93.75</v>
       </c>
       <c r="G2">
-        <v>29.41</v>
+        <v>6.25</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>7.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2211,7 +2211,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>41</v>
@@ -2220,19 +2220,19 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="G3">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2243,28 +2243,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>42</v>
       </c>
       <c r="C4">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2275,16 +2275,16 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>43</v>
       </c>
       <c r="C5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>6.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2307,16 +2307,16 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>44</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -2328,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>45</v>
@@ -2360,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2764,7 +2764,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2808,150 +2808,12 @@
         <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920145</v>
-      </c>
-      <c r="B3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920135</v>
-      </c>
-      <c r="B4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920141</v>
-      </c>
-      <c r="B5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920143</v>
-      </c>
-      <c r="B6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920381</v>
-      </c>
-      <c r="B7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920147</v>
-      </c>
-      <c r="B8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8">
         <v>5</v>
       </c>
     </row>
